--- a/exotic-birds-shop/public/catalog.xlsx
+++ b/exotic-birds-shop/public/catalog.xlsx
@@ -1,62 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguel/Development/POCs/aves-massapez/exotic-birds-shop/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelduarte/Development/repos/aves-massapez/exotic-birds-shop/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217F1A07-05D9-8945-B86E-0E68C74E047C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B4295B-4F12-2F4D-8B09-2B1655C5159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="500" windowWidth="30240" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Base Price</t>
-  </si>
-  <si>
-    <t>Image</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>Colors</t>
-  </si>
-  <si>
-    <t>Ages</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="76">
+  <si>
+    <t>SpeciesID</t>
+  </si>
+  <si>
+    <t>SpeciesName_PT</t>
+  </si>
+  <si>
+    <t>SpeciesName_EN</t>
+  </si>
+  <si>
+    <t>SpeciesBasePrice</t>
+  </si>
+  <si>
+    <t>SpeciesEggPrice</t>
+  </si>
+  <si>
+    <t>SpeciesImage</t>
+  </si>
+  <si>
+    <t>SpeciesDescription_PT</t>
+  </si>
+  <si>
+    <t>SpeciesDescription_EN</t>
+  </si>
+  <si>
+    <t>SpeciesStock</t>
+  </si>
+  <si>
+    <t>ColorID</t>
+  </si>
+  <si>
+    <t>ColorName_PT</t>
+  </si>
+  <si>
+    <t>ColorName_EN</t>
+  </si>
+  <si>
+    <t>BirthDate</t>
+  </si>
+  <si>
+    <t>AgeCategoryOverride</t>
+  </si>
+  <si>
+    <t>VariantPrice</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Sold</t>
+  </si>
+  <si>
+    <t>VariantImage</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
   <si>
     <t>pavoes-azuis</t>
@@ -65,19 +85,76 @@
     <t>Pavões Azuis</t>
   </si>
   <si>
+    <t>Blue Peacocks</t>
+  </si>
+  <si>
     <t>./assets/images/pavoes_azuis.jpg</t>
   </si>
   <si>
-    <t>Lindos pavões azuis criados com muito cuidado e carinho. Aves saudáveis e bem socializadas.</t>
+    <t>Lindos pavões azuis criados com cuidado e carinho. Aves saudáveis e bem socializadas.</t>
+  </si>
+  <si>
+    <t>Beautiful blue peacocks raised with great care and affection. Healthy and well-socialized birds.</t>
   </si>
   <si>
     <t>in</t>
   </si>
   <si>
-    <t>[{"id":"blue","name":"Azul Tradicional","priceModifier":0},{"id":"royal-blue","name":"Azul Real","priceModifier":30},{"id":"peacock-green","name":"Verde Pavão","priceModifier":20}]</t>
-  </si>
-  <si>
-    <t>[{"id":"young","name":"Jovem (3-6 meses)","priceModifier":0},{"id":"adult","name":"Adulto (6-12 meses)","priceModifier":50},{"id":"mature","name":"Adulto (1+ anos)","priceModifier":80}]</t>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>Azul Tradicional</t>
+  </si>
+  <si>
+    <t>Traditional Blue</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>egg</t>
+  </si>
+  <si>
+    <t>Lote fresco para incubação imediata.</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Criação em recinto exterior.</t>
+  </si>
+  <si>
+    <t>royal-blue</t>
+  </si>
+  <si>
+    <t>Azul Real</t>
+  </si>
+  <si>
+    <t>Royal Blue</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>Seleção azul real com plumagem intensa.</t>
+  </si>
+  <si>
+    <t>peacock-green</t>
+  </si>
+  <si>
+    <t>Verde Pavão</t>
+  </si>
+  <si>
+    <t>Peacock Green</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>Variante verde pavão rara.</t>
   </si>
   <si>
     <t>arara</t>
@@ -86,19 +163,52 @@
     <t>Arara Vermelha</t>
   </si>
   <si>
+    <t>Red Macaw</t>
+  </si>
+  <si>
     <t>./assets/images/arara.jpeg</t>
   </si>
   <si>
     <t>Majestosa arara vermelha, ave símbolo da fauna brasileira.</t>
   </si>
   <si>
+    <t>Majestic red macaw, symbolic bird of Brazilian fauna.</t>
+  </si>
+  <si>
     <t>low</t>
   </si>
   <si>
-    <t>[{"id":"red","name":"Vermelho Clássico","priceModifier":0},{"id":"scarlet","name":"Escarlate","priceModifier":100}]</t>
-  </si>
-  <si>
-    <t>[{"id":"young","name":"Jovem (6-12 meses)","priceModifier":0},{"id":"adult","name":"Adulto (1-2 anos)","priceModifier":300}]</t>
+    <t>red</t>
+  </si>
+  <si>
+    <t>Vermelho Clássico</t>
+  </si>
+  <si>
+    <t>Classic Red</t>
+  </si>
+  <si>
+    <t>Ovos recolhidos esta semana.</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>Juvenis com treino inicial de socialização.</t>
+  </si>
+  <si>
+    <t>scarlet</t>
+  </si>
+  <si>
+    <t>Escarlate</t>
+  </si>
+  <si>
+    <t>Scarlet</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
+    <t>Adulto escarlate pronto para reprodução.</t>
   </si>
   <si>
     <t>papagaio</t>
@@ -107,19 +217,37 @@
     <t>Papagaio Cinzento</t>
   </si>
   <si>
+    <t>African Grey Parrot</t>
+  </si>
+  <si>
     <t>./assets/images/papagaio.jpeg</t>
   </si>
   <si>
     <t>Papagaio cinzento africano, conhecido pela inteligência.</t>
   </si>
   <si>
+    <t>African grey parrot, known for its intelligence.</t>
+  </si>
+  <si>
     <t>out</t>
   </si>
   <si>
-    <t>[{"id":"grey","name":"Cinzento","priceModifier":0}]</t>
-  </si>
-  <si>
-    <t>[{"id":"young","name":"Jovem (4-8 meses)","priceModifier":0},{"id":"adult","name":"Adulto (8+ meses)","priceModifier":150}]</t>
+    <t>grey</t>
+  </si>
+  <si>
+    <t>Cinzento</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>Disponível apenas para incubação monitorizada.</t>
+  </si>
+  <si>
+    <t>2025-04-20</t>
+  </si>
+  <si>
+    <t>Jovem com vocalização inicial.</t>
   </si>
 </sst>
 </file>
@@ -496,19 +624,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="8" width="40" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="8" width="52" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="36" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,90 +668,575 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>120</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>150</v>
+      </c>
+      <c r="E2">
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2">
+        <v>55</v>
+      </c>
+      <c r="P2">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>150</v>
+      </c>
+      <c r="E3">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3">
+        <v>150</v>
+      </c>
+      <c r="P3">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4">
+        <v>185</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>150</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5">
+        <v>195</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6">
         <v>2400</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
+      <c r="E6">
+        <v>1200</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6">
+        <v>1300</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7">
+        <v>2400</v>
+      </c>
+      <c r="E7">
+        <v>1200</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7">
+        <v>2650</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>48</v>
+      </c>
+      <c r="S7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8">
+        <v>2400</v>
+      </c>
+      <c r="E8">
+        <v>1200</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8">
+        <v>2900</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9">
         <v>800</v>
       </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
+      <c r="E9">
+        <v>400</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9">
+        <v>420</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10">
+        <v>800</v>
+      </c>
+      <c r="E10">
+        <v>400</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" t="s">
+        <v>71</v>
+      </c>
+      <c r="L10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" t="s">
+        <v>74</v>
+      </c>
+      <c r="N10" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10">
+        <v>950</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="s">
+        <v>66</v>
+      </c>
+      <c r="S10" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:S8 A10:P10 R10:S10 A9:P9 R9:S9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>